--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484300_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484300_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.457</v>
+        <v>6.0019</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9162</v>
+        <v>5.5428</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.4591</v>
       </c>
       <c r="G2" t="n">
         <v>1.6755</v>
@@ -610,13 +610,13 @@
         <v>4.1022</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4176</v>
+        <v>0.1273</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9462</v>
+        <v>-0.3196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5286</v>
+        <v>0.4469</v>
       </c>
       <c r="V2" t="n">
         <v>2.0503</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6441</v>
+        <v>4.7107</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9178</v>
+        <v>4.0388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7264</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>2.1272</v>
@@ -688,13 +688,13 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0225</v>
+        <v>0.044</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0221</v>
+        <v>0.1432</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0447</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6653</v>
+        <v>1.502</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6173</v>
+        <v>1.345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0481</v>
+        <v>0.157</v>
       </c>
       <c r="G4" t="n">
         <v>0.4674</v>
@@ -766,13 +766,13 @@
         <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7554999999999999</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0756</v>
+        <v>-0.3479</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3201</v>
+        <v>0.4291</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6093</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2878</v>
+        <v>0.315</v>
       </c>
       <c r="E5" t="n">
         <v>-0.0605</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3483</v>
+        <v>0.3756</v>
       </c>
       <c r="G5" t="n">
         <v>0.2696</v>
@@ -844,13 +844,13 @@
         <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1772</v>
+        <v>-0.15</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1167</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6403</v>
+        <v>-0.0252</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6925</v>
+        <v>-0.2681</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0522</v>
+        <v>0.2428</v>
       </c>
       <c r="G6" t="n">
         <v>-2.6133</v>
@@ -922,13 +922,13 @@
         <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0036</v>
+        <v>-0.3886</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5915</v>
+        <v>-0.1671</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4122</v>
+        <v>-0.2215</v>
       </c>
       <c r="V6" t="n">
         <v>1.2186</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1452</v>
+        <v>-1.0441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2874</v>
+        <v>0.3885</v>
       </c>
       <c r="F7" t="n">
         <v>-1.4326</v>
@@ -1000,10 +1000,10 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.99</v>
+        <v>-2.6173</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5505</v>
+        <v>-3.7776</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4396</v>
+        <v>1.1603</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1425</v>
+        <v>-2.0139</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0906</v>
+        <v>-0.9077</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0519</v>
+        <v>-1.1062</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5332</v>
+        <v>0.1738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9657</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5675</v>
+        <v>0.1086</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.6757</v>
+        <v>-2.1876</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0563</v>
+        <v>-0.9729</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6194</v>
+        <v>-1.2148</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0353</v>
+        <v>-0.0956</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6299</v>
+        <v>-0.0446</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6651</v>
+        <v>-0.051</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2735</v>
+        <v>0.6642</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7731</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2057</v>
+        <v>-2.7363</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1208</v>
+        <v>-0.1061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9152</v>
+        <v>-2.6302</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0139</v>
+        <v>-2.1425</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9077</v>
+        <v>-1.0906</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1062</v>
+        <v>-1.0519</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1738</v>
+        <v>1.5332</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.9657</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1086</v>
+        <v>0.5675</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1876</v>
+        <v>-3.6757</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9729</v>
+        <v>-2.0563</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2148</v>
+        <v>-1.6194</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6839</v>
+        <v>0.2889</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3878</v>
+        <v>-0.1855</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2961</v>
+        <v>0.4745</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6642</v>
+        <v>-1.2735</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.4996</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6642</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2693</v>
+        <v>-4.2804</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0682</v>
+        <v>-4.0794</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2011</v>
@@ -1234,10 +1234,10 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2685</v>
+        <v>0.2573</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2355</v>
+        <v>0.2244</v>
       </c>
       <c r="U10" t="n">
         <v>0.033</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8301</v>
+        <v>-4.6421</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0298</v>
+        <v>-6.5966</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1996</v>
+        <v>1.9545</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5362</v>
@@ -1312,13 +1312,13 @@
         <v>3.1255</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4874</v>
+        <v>0.6755</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8999</v>
+        <v>0.3331</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5875</v>
+        <v>0.3424</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.026400000000002</v>
+        <v>-2.8158</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.783600000000002</v>
+        <v>-3.5732</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7573000000000001</v>
+        <v>0.7572999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-11.7876</v>
@@ -1390,13 +1390,13 @@
         <v>21.4877</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3295999999999997</v>
+        <v>0.8805999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5945</v>
+        <v>-0.3839000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2646</v>
+        <v>1.2649</v>
       </c>
       <c r="V12" t="n">
         <v>0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9777</v>
+        <v>7.7178</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5807</v>
+        <v>4.1874</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3969</v>
+        <v>3.5304</v>
       </c>
       <c r="G13" t="n">
         <v>7.0211</v>
@@ -1468,13 +1468,13 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2148</v>
+        <v>0.5254</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8335</v>
+        <v>-0.2269</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6188</v>
+        <v>0.7523</v>
       </c>
       <c r="V13" t="n">
         <v>3.1014</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4155</v>
+        <v>6.9381</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0211</v>
+        <v>3.92</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3944</v>
+        <v>3.0181</v>
       </c>
       <c r="G14" t="n">
         <v>7.8825</v>
@@ -1546,13 +1546,13 @@
         <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1079</v>
+        <v>0.4147</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1905</v>
+        <v>0.4332</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1638</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9791</v>
+        <v>1.9247</v>
       </c>
       <c r="E15" t="n">
         <v>1.9224</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0568</v>
+        <v>0.0023</v>
       </c>
       <c r="G15" t="n">
         <v>1.8477</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1315</v>
+        <v>0.077</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1315</v>
+        <v>0.077</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5839</v>
+        <v>1.1199</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7735</v>
+        <v>-0.8577</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1896</v>
+        <v>1.9776</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0337</v>
+        <v>2.6892</v>
       </c>
       <c r="H16" t="n">
-        <v>1.547</v>
+        <v>0.7608</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5132</v>
+        <v>1.9283</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7418</v>
+        <v>3.3237</v>
       </c>
       <c r="K16" t="n">
-        <v>2.58</v>
+        <v>1.3942</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1619</v>
+        <v>1.9295</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7081</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.033</v>
+        <v>-0.6334</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6751</v>
+        <v>-0.0012</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.46</v>
+        <v>0.0213</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0083</v>
+        <v>-0.2468</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4516</v>
+        <v>0.2681</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4959</v>
+        <v>0.1675</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1685</v>
+        <v>0.1638</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7533</v>
+        <v>1.5712</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5848</v>
+        <v>-1.4075</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7564</v>
+        <v>1.0337</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6887</v>
+        <v>1.547</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0677</v>
+        <v>-0.5132</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5007</v>
+        <v>2.7418</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7585</v>
+        <v>2.58</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7422</v>
+        <v>0.1619</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2571</v>
+        <v>-1.7081</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4472</v>
+        <v>-1.033</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8099</v>
+        <v>-0.6751</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3621</v>
+        <v>0.0399</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5614</v>
+        <v>-0.1939</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1993</v>
+        <v>0.2337</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1571</v>
+        <v>-0.1751</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5655</v>
+        <v>0.2477</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4084</v>
+        <v>-0.4228</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6892</v>
+        <v>-0.7564</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7608</v>
+        <v>-0.6887</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9283</v>
+        <v>-0.0677</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3237</v>
+        <v>1.5007</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3942</v>
+        <v>0.7585</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9295</v>
+        <v>0.7422</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-2.2571</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6334</v>
+        <v>-1.4472</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0012</v>
+        <v>-0.8099</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.1022</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2557</v>
+        <v>0.0186</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9546</v>
+        <v>0.0558</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3012</v>
+        <v>-0.0373</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1675</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1675</v>
+        <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3257</v>
+        <v>-0.6304</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7655</v>
+        <v>-2.0688</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4397</v>
+        <v>1.4384</v>
       </c>
       <c r="G19" t="n">
         <v>0.0017</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8446</v>
+        <v>0.5399</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5668</v>
+        <v>0.2635</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2778</v>
+        <v>0.2764</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.416</v>
+        <v>-1.2877</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1197</v>
+        <v>-1.0186</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2964</v>
+        <v>-0.2691</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2272</v>
@@ -2014,13 +2014,13 @@
         <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0837</v>
+        <v>0.0447</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2794</v>
+        <v>0.3067</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4959</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2871</v>
+        <v>-2.409</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2368</v>
+        <v>-1.439</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0503</v>
+        <v>-0.97</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0322</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0363</v>
+        <v>-0.1582</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0522</v>
+        <v>-0.2544</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0159</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7801</v>
+        <v>-2.994</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7181</v>
+        <v>-2.1225</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0621</v>
+        <v>-0.8714</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4974</v>
@@ -2170,13 +2170,13 @@
         <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4986</v>
+        <v>0.2848</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5063</v>
+        <v>0.1018</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0077</v>
+        <v>0.1829</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1321</v>
+        <v>-4.9935</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4027</v>
+        <v>-5.0994</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2706</v>
+        <v>0.1059</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1752</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2686</v>
+        <v>-0.13</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5182</v>
+        <v>0.3534</v>
       </c>
       <c r="V23" t="n">
         <v>2.4373</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.026599999999999</v>
+        <v>5.374600000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7573000000000008</v>
+        <v>-0.7572999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>4.7836</v>
+        <v>6.131900000000002</v>
       </c>
       <c r="G24" t="n">
         <v>11.7875</v>
@@ -2302,22 +2302,22 @@
         <v>16.7307</v>
       </c>
       <c r="K24" t="n">
-        <v>9.306799999999999</v>
+        <v>9.306799999999997</v>
       </c>
       <c r="L24" t="n">
-        <v>7.424100000000003</v>
+        <v>7.424099999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-4.9432</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.937200000000001</v>
+        <v>-4.9372</v>
       </c>
       <c r="O24" t="n">
         <v>-0.005999999999999894</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.813600000000001</v>
+        <v>-7.813599999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-21.4878</v>
@@ -2326,16 +2326,16 @@
         <v>13.674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3298</v>
+        <v>1.6781</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2648</v>
+        <v>-1.2649</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5945</v>
+        <v>2.9426</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2772999999999999</v>
+        <v>-0.2772999999999994</v>
       </c>
       <c r="W24" t="n">
         <v>5.2644</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484300_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484300_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-5.264399999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,11 +1541,16 @@
       <c r="X13" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,28 +1562,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9381</v>
+        <v>6.6311</v>
       </c>
       <c r="E14" t="n">
-        <v>3.92</v>
+        <v>3.613</v>
       </c>
       <c r="F14" t="n">
         <v>3.0181</v>
       </c>
       <c r="G14" t="n">
-        <v>7.8825</v>
+        <v>7.5755</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9867</v>
+        <v>2.6797</v>
       </c>
       <c r="I14" t="n">
         <v>4.8958</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4193</v>
+        <v>6.1123</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6017</v>
+        <v>2.2947</v>
       </c>
       <c r="L14" t="n">
         <v>3.8176</v>
@@ -1562,12 +1623,17 @@
       </c>
       <c r="X14" t="n">
         <v>-0.8317</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,37 +1645,37 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9247</v>
+        <v>2.7489</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9224</v>
+        <v>2.7489</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0023</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8477</v>
+        <v>2.7489</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0542</v>
+        <v>1.5349</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9019</v>
+        <v>1.214</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9224</v>
+        <v>2.7489</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0205</v>
+        <v>1.5349</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9019</v>
+        <v>1.214</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1624,13 +1690,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1640,12 +1706,17 @@
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1199</v>
+        <v>1.9247</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8577</v>
+        <v>1.9224</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9776</v>
+        <v>0.0023</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6892</v>
+        <v>1.8477</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7608</v>
+        <v>-0.0542</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9283</v>
+        <v>1.9019</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3237</v>
+        <v>1.9224</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3942</v>
+        <v>0.0205</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9295</v>
+        <v>1.9019</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6334</v>
+        <v>-0.0747</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0213</v>
+        <v>0.077</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2468</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2681</v>
+        <v>0.077</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1638</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5712</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4075</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0337</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>1.547</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5132</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7418</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>2.58</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7081</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.033</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6751</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0399</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2337</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1751</v>
+        <v>0.1638</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2477</v>
+        <v>1.5712</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4228</v>
+        <v>-1.4075</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7564</v>
+        <v>1.0337</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6887</v>
+        <v>1.547</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0677</v>
+        <v>-0.5132</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5007</v>
+        <v>2.7418</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7585</v>
+        <v>2.58</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7422</v>
+        <v>0.1619</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2571</v>
+        <v>-1.7081</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4472</v>
+        <v>-1.033</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8099</v>
+        <v>-0.6751</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0186</v>
+        <v>0.0399</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0558</v>
+        <v>-0.1939</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0373</v>
+        <v>0.2337</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6304</v>
+        <v>-0.1751</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0688</v>
+        <v>0.2477</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4384</v>
+        <v>-0.4228</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0017</v>
+        <v>-0.7564</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1095</v>
+        <v>-0.6887</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1078</v>
+        <v>-0.0677</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1835</v>
+        <v>1.5007</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3287</v>
+        <v>0.7585</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5122</v>
+        <v>0.7422</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1852</v>
+        <v>-2.2571</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2192</v>
+        <v>-1.4472</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4045</v>
+        <v>-0.8099</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5399</v>
+        <v>0.0186</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2635</v>
+        <v>0.0558</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2764</v>
+        <v>-0.0373</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2877</v>
+        <v>-0.6304</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0186</v>
+        <v>-2.0688</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2691</v>
+        <v>1.4384</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2272</v>
+        <v>0.0017</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.1095</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2965</v>
+        <v>-0.1078</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.1835</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9184</v>
+        <v>0.3287</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1619</v>
+        <v>-0.5122</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5294</v>
+        <v>0.1852</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3948</v>
+        <v>-0.2192</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1346</v>
+        <v>0.4045</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0447</v>
+        <v>0.5399</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.262</v>
+        <v>0.2635</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3067</v>
+        <v>0.2764</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.409</v>
+        <v>-1.2877</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.439</v>
+        <v>-1.0186</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.97</v>
+        <v>-0.2691</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0322</v>
+        <v>-0.2272</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2653</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7669</v>
+        <v>0.2965</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1846</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0422</v>
+        <v>-0.9184</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2268</v>
+        <v>0.1619</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8476</v>
+        <v>0.5294</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3075</v>
+        <v>0.3948</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5401</v>
+        <v>0.1346</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1582</v>
+        <v>0.0447</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2544</v>
+        <v>-0.262</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.3067</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.994</v>
+        <v>-1.629</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1225</v>
+        <v>-3.6066</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8714</v>
+        <v>1.9776</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4974</v>
+        <v>-0.0597</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.7741</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5659</v>
+        <v>0.7144</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3528</v>
+        <v>0.5748</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3479</v>
+        <v>-0.1407</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7007</v>
+        <v>0.7156</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1445</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2793</v>
+        <v>-0.6334</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1348</v>
+        <v>-0.0012</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>-4.1022</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2848</v>
+        <v>0.0213</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1018</v>
+        <v>-0.2468</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1829</v>
+        <v>0.2681</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>0.1675</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9935</v>
+        <v>-2.409</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0994</v>
+        <v>-1.439</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1059</v>
+        <v>-0.97</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1752</v>
+        <v>-3.0322</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6938</v>
+        <v>-1.2653</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4814</v>
+        <v>-1.7669</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1463</v>
+        <v>-1.1846</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2049</v>
+        <v>0.0422</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9414</v>
+        <v>-1.2268</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0289</v>
+        <v>-1.8476</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4889</v>
+        <v>-1.3075</v>
       </c>
       <c r="O23" t="n">
         <v>-0.5401</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1255</v>
+        <v>0.7814</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.13</v>
+        <v>-0.1582</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4835</v>
+        <v>-0.2544</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3534</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.374600000000002</v>
+        <v>-2.994</v>
       </c>
       <c r="E24" t="n">
+        <v>-2.1225</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.8714</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.4974</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5659</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.3528</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.7007</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2793</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. GEORGIOU</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.9935</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.0994</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.1752</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.6938</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.4814</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.1463</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.2049</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.9414</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.0289</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5401</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4835</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484300_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5.374599999999998</v>
+      </c>
+      <c r="E26" t="n">
         <v>-0.7572999999999999</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>6.131900000000002</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>11.7875</v>
       </c>
-      <c r="H24" t="n">
-        <v>4.369499999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>7.4181</v>
-      </c>
-      <c r="J24" t="n">
-        <v>16.7307</v>
-      </c>
-      <c r="K24" t="n">
-        <v>9.306799999999997</v>
-      </c>
-      <c r="L24" t="n">
-        <v>7.424099999999999</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="H26" t="n">
+        <v>4.3695</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.4182</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16.73070000000001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9.306799999999996</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.424199999999999</v>
+      </c>
+      <c r="M26" t="n">
         <v>-4.9432</v>
       </c>
-      <c r="N24" t="n">
-        <v>-4.9372</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N26" t="n">
+        <v>-4.937200000000001</v>
+      </c>
+      <c r="O26" t="n">
         <v>-0.005999999999999894</v>
       </c>
-      <c r="P24" t="n">
-        <v>-7.813599999999999</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="P26" t="n">
+        <v>-7.813600000000001</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-21.4878</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>13.674</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>1.6781</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-1.2649</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>2.9426</v>
       </c>
-      <c r="V24" t="n">
-        <v>-0.2772999999999994</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="V26" t="n">
+        <v>-0.2772999999999999</v>
+      </c>
+      <c r="W26" t="n">
         <v>5.2644</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-5.5417</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
